--- a/data/nzd0416/nzd0416.xlsx
+++ b/data/nzd0416/nzd0416.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K726"/>
+  <dimension ref="A1:K727"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28718,6 +28718,45 @@
         <v>303.81</v>
       </c>
       <c r="K726" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:14:13+00:00</t>
+        </is>
+      </c>
+      <c r="B727" t="n">
+        <v>316.58</v>
+      </c>
+      <c r="C727" t="n">
+        <v>312.21</v>
+      </c>
+      <c r="D727" t="n">
+        <v>307.24</v>
+      </c>
+      <c r="E727" t="n">
+        <v>314.41</v>
+      </c>
+      <c r="F727" t="n">
+        <v>310.21</v>
+      </c>
+      <c r="G727" t="n">
+        <v>321.52</v>
+      </c>
+      <c r="H727" t="n">
+        <v>318.31</v>
+      </c>
+      <c r="I727" t="n">
+        <v>317.82</v>
+      </c>
+      <c r="J727" t="n">
+        <v>315.71</v>
+      </c>
+      <c r="K727" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28734,7 +28773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B818"/>
+  <dimension ref="A1:B819"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36917,6 +36956,16 @@
       </c>
       <c r="B818" t="n">
         <v>0.21</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B819" t="n">
+        <v>0.27</v>
       </c>
     </row>
   </sheetData>
@@ -37085,28 +37134,28 @@
         <v>0.0689</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6225060849541547</v>
+        <v>-0.6221487095217463</v>
       </c>
       <c r="J2" t="n">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="K2" t="n">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0826893979932789</v>
+        <v>0.08282671442905754</v>
       </c>
       <c r="M2" t="n">
-        <v>13.39617194160954</v>
+        <v>13.37971515427385</v>
       </c>
       <c r="N2" t="n">
-        <v>245.1612212623645</v>
+        <v>244.8259883540688</v>
       </c>
       <c r="O2" t="n">
-        <v>15.65762501985421</v>
+        <v>15.64691625701591</v>
       </c>
       <c r="P2" t="n">
-        <v>331.6268395555026</v>
+        <v>331.6232324391486</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -37163,28 +37212,28 @@
         <v>0.07149999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.7908198408390863</v>
+        <v>-0.7910748407946085</v>
       </c>
       <c r="J3" t="n">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="K3" t="n">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07415782329425569</v>
+        <v>0.07440602597326562</v>
       </c>
       <c r="M3" t="n">
-        <v>17.54223735332661</v>
+        <v>17.51933709969991</v>
       </c>
       <c r="N3" t="n">
-        <v>445.2799007867786</v>
+        <v>444.6678173700236</v>
       </c>
       <c r="O3" t="n">
-        <v>21.10165635173643</v>
+        <v>21.08714815640142</v>
       </c>
       <c r="P3" t="n">
-        <v>333.9817258584329</v>
+        <v>333.9842996629712</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37241,28 +37290,28 @@
         <v>0.06660000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6326967422415161</v>
+        <v>-0.6324387686705698</v>
       </c>
       <c r="J4" t="n">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="K4" t="n">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02520908831727131</v>
+        <v>0.02526221598339018</v>
       </c>
       <c r="M4" t="n">
-        <v>25.75147574201398</v>
+        <v>25.7172107159602</v>
       </c>
       <c r="N4" t="n">
-        <v>875.3671159365111</v>
+        <v>874.1576374334076</v>
       </c>
       <c r="O4" t="n">
-        <v>29.58660365666379</v>
+        <v>29.56615696084642</v>
       </c>
       <c r="P4" t="n">
-        <v>322.9347957920502</v>
+        <v>322.9321736412369</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37319,28 +37368,28 @@
         <v>0.07149999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7037358965642661</v>
+        <v>-0.7027855032795428</v>
       </c>
       <c r="J5" t="n">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="K5" t="n">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04217374237960703</v>
+        <v>0.04218378743898088</v>
       </c>
       <c r="M5" t="n">
-        <v>21.94305068439243</v>
+        <v>21.91762894839339</v>
       </c>
       <c r="N5" t="n">
-        <v>635.9923552301969</v>
+        <v>635.1310621415944</v>
       </c>
       <c r="O5" t="n">
-        <v>25.21888885796115</v>
+        <v>25.20180672375682</v>
       </c>
       <c r="P5" t="n">
-        <v>329.4019110364659</v>
+        <v>329.3922552568645</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37397,28 +37446,28 @@
         <v>0.0738</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7312292060836703</v>
+        <v>-0.729967283609394</v>
       </c>
       <c r="J6" t="n">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="K6" t="n">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04118792950085626</v>
+        <v>0.04116743650622823</v>
       </c>
       <c r="M6" t="n">
-        <v>23.12310987946362</v>
+        <v>23.09775476081858</v>
       </c>
       <c r="N6" t="n">
-        <v>703.8149368994887</v>
+        <v>702.8730516371888</v>
       </c>
       <c r="O6" t="n">
-        <v>26.52951067960901</v>
+        <v>26.51175308494685</v>
       </c>
       <c r="P6" t="n">
-        <v>324.7705453315598</v>
+        <v>324.7577244862512</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37475,28 +37524,28 @@
         <v>0.07820000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5624525057847105</v>
+        <v>-0.5617575069451194</v>
       </c>
       <c r="J7" t="n">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="K7" t="n">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04962986265910019</v>
+        <v>0.0496524514149943</v>
       </c>
       <c r="M7" t="n">
-        <v>15.98440838633523</v>
+        <v>15.96583444525203</v>
       </c>
       <c r="N7" t="n">
-        <v>342.5384347705909</v>
+        <v>342.0744862472249</v>
       </c>
       <c r="O7" t="n">
-        <v>18.50779389258998</v>
+        <v>18.49525577674515</v>
       </c>
       <c r="P7" t="n">
-        <v>333.7466479509798</v>
+        <v>333.7395869208502</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37553,28 +37602,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4560842146016572</v>
+        <v>-0.4556071884198095</v>
       </c>
       <c r="J8" t="n">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="K8" t="n">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02685886255962433</v>
+        <v>0.0268817523192959</v>
       </c>
       <c r="M8" t="n">
-        <v>17.8568365316466</v>
+        <v>17.83462340797052</v>
       </c>
       <c r="N8" t="n">
-        <v>426.1536243992236</v>
+        <v>425.5693348452349</v>
       </c>
       <c r="O8" t="n">
-        <v>20.64348866832405</v>
+        <v>20.62933190496568</v>
       </c>
       <c r="P8" t="n">
-        <v>328.5484654783664</v>
+        <v>328.5436190008606</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37631,28 +37680,28 @@
         <v>0.06270000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3948934472311765</v>
+        <v>-0.3945794381285208</v>
       </c>
       <c r="J9" t="n">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="K9" t="n">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01800340230607211</v>
+        <v>0.0180278793983929</v>
       </c>
       <c r="M9" t="n">
-        <v>18.96401026789108</v>
+        <v>18.93940981928169</v>
       </c>
       <c r="N9" t="n">
-        <v>480.953556019707</v>
+        <v>480.2911276168303</v>
       </c>
       <c r="O9" t="n">
-        <v>21.93065334229026</v>
+        <v>21.91554534153395</v>
       </c>
       <c r="P9" t="n">
-        <v>327.0502620975481</v>
+        <v>327.047071836488</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37709,28 +37758,28 @@
         <v>0.0471</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4202419251702164</v>
+        <v>-0.4204811221049798</v>
       </c>
       <c r="J10" t="n">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="K10" t="n">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01392722510150746</v>
+        <v>0.01398357541749951</v>
       </c>
       <c r="M10" t="n">
-        <v>23.1454343938622</v>
+        <v>23.11449685111943</v>
       </c>
       <c r="N10" t="n">
-        <v>719.2988262924003</v>
+        <v>718.2995232774402</v>
       </c>
       <c r="O10" t="n">
-        <v>26.81974694683752</v>
+        <v>26.8011104859004</v>
       </c>
       <c r="P10" t="n">
-        <v>327.6732585393781</v>
+        <v>327.6756649686168</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37768,7 +37817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K726"/>
+  <dimension ref="A1:K727"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79073,6 +79122,63 @@
         </is>
       </c>
     </row>
+    <row r="727">
+      <c r="A727" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:14:13+00:00</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>-43.04865786586472,173.07190056591278</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>-43.04848713801028,173.0710314326363</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>-43.048308974154196,173.0701478800817</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>-43.04828189544554,173.06921407615428</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>-43.04821859762018,173.06829662960374</t>
+        </is>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>-43.048304445748634,173.06738212225224</t>
+        </is>
+      </c>
+      <c r="H727" t="inlineStr">
+        <is>
+          <t>-43.04830661427636,173.06647225845464</t>
+        </is>
+      </c>
+      <c r="I727" t="inlineStr">
+        <is>
+          <t>-43.04833303303622,173.0655746462515</t>
+        </is>
+      </c>
+      <c r="J727" t="inlineStr">
+        <is>
+          <t>-43.048344880146395,173.06467608872717</t>
+        </is>
+      </c>
+      <c r="K727" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0416/nzd0416.xlsx
+++ b/data/nzd0416/nzd0416.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K727"/>
+  <dimension ref="A1:K730"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28759,6 +28759,123 @@
       <c r="K727" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:07:53+00:00</t>
+        </is>
+      </c>
+      <c r="B728" t="n">
+        <v>317.18</v>
+      </c>
+      <c r="C728" t="n">
+        <v>312.98</v>
+      </c>
+      <c r="D728" t="n">
+        <v>308.57</v>
+      </c>
+      <c r="E728" t="n">
+        <v>315.68</v>
+      </c>
+      <c r="F728" t="n">
+        <v>311.82</v>
+      </c>
+      <c r="G728" t="n">
+        <v>322.71</v>
+      </c>
+      <c r="H728" t="n">
+        <v>319.68</v>
+      </c>
+      <c r="I728" t="n">
+        <v>318.98</v>
+      </c>
+      <c r="J728" t="n">
+        <v>317.35</v>
+      </c>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:14:06+00:00</t>
+        </is>
+      </c>
+      <c r="B729" t="n">
+        <v>318.56</v>
+      </c>
+      <c r="C729" t="n">
+        <v>315.3</v>
+      </c>
+      <c r="D729" t="n">
+        <v>311.77</v>
+      </c>
+      <c r="E729" t="n">
+        <v>318.87</v>
+      </c>
+      <c r="F729" t="n">
+        <v>316.01</v>
+      </c>
+      <c r="G729" t="n">
+        <v>325.62</v>
+      </c>
+      <c r="H729" t="n">
+        <v>322.39</v>
+      </c>
+      <c r="I729" t="n">
+        <v>321.57</v>
+      </c>
+      <c r="J729" t="n">
+        <v>320.48</v>
+      </c>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:07:44+00:00</t>
+        </is>
+      </c>
+      <c r="B730" t="n">
+        <v>319.06</v>
+      </c>
+      <c r="C730" t="n">
+        <v>315.89</v>
+      </c>
+      <c r="D730" t="n">
+        <v>312.84</v>
+      </c>
+      <c r="E730" t="n">
+        <v>319.98</v>
+      </c>
+      <c r="F730" t="n">
+        <v>317.54</v>
+      </c>
+      <c r="G730" t="n">
+        <v>326.51</v>
+      </c>
+      <c r="H730" t="n">
+        <v>323.71</v>
+      </c>
+      <c r="I730" t="n">
+        <v>322.73</v>
+      </c>
+      <c r="J730" t="n">
+        <v>322.03</v>
+      </c>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -28773,7 +28890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B819"/>
+  <dimension ref="A1:B822"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36966,6 +37083,36 @@
       </c>
       <c r="B819" t="n">
         <v>0.27</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B820" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B821" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B822" t="n">
+        <v>0.83</v>
       </c>
     </row>
   </sheetData>
@@ -37134,28 +37281,28 @@
         <v>0.0689</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6221487095217463</v>
+        <v>-0.6197350095727854</v>
       </c>
       <c r="J2" t="n">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="K2" t="n">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08282671442905754</v>
+        <v>0.08289597662606252</v>
       </c>
       <c r="M2" t="n">
-        <v>13.37971515427385</v>
+        <v>13.33820245973358</v>
       </c>
       <c r="N2" t="n">
-        <v>244.8259883540688</v>
+        <v>243.858739222552</v>
       </c>
       <c r="O2" t="n">
-        <v>15.64691625701591</v>
+        <v>15.61597704988554</v>
       </c>
       <c r="P2" t="n">
-        <v>331.6232324391486</v>
+        <v>331.5988294466263</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -37212,28 +37359,28 @@
         <v>0.07149999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.7910748407946085</v>
+        <v>-0.7898085912008009</v>
       </c>
       <c r="J3" t="n">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="K3" t="n">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07440602597326562</v>
+        <v>0.07479321391993765</v>
       </c>
       <c r="M3" t="n">
-        <v>17.51933709969991</v>
+        <v>17.45449998165669</v>
       </c>
       <c r="N3" t="n">
-        <v>444.6678173700236</v>
+        <v>442.8548828424173</v>
       </c>
       <c r="O3" t="n">
-        <v>21.08714815640142</v>
+        <v>21.04411753536882</v>
       </c>
       <c r="P3" t="n">
-        <v>333.9842996629712</v>
+        <v>333.9714913303508</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37290,28 +37437,28 @@
         <v>0.06660000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6324387686705698</v>
+        <v>-0.6286019407772983</v>
       </c>
       <c r="J4" t="n">
+        <v>729</v>
+      </c>
+      <c r="K4" t="n">
         <v>726</v>
       </c>
-      <c r="K4" t="n">
-        <v>723</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.02526221598339018</v>
+        <v>0.02517825179811206</v>
       </c>
       <c r="M4" t="n">
-        <v>25.7172107159602</v>
+        <v>25.63090543761761</v>
       </c>
       <c r="N4" t="n">
-        <v>874.1576374334076</v>
+        <v>870.6530359053527</v>
       </c>
       <c r="O4" t="n">
-        <v>29.56615696084642</v>
+        <v>29.506830326305</v>
       </c>
       <c r="P4" t="n">
-        <v>322.9321736412369</v>
+        <v>322.893105700974</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37368,28 +37515,28 @@
         <v>0.07149999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7027855032795428</v>
+        <v>-0.696940346848784</v>
       </c>
       <c r="J5" t="n">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="K5" t="n">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04218378743898088</v>
+        <v>0.04185425517086949</v>
       </c>
       <c r="M5" t="n">
-        <v>21.91762894839339</v>
+        <v>21.85701635525201</v>
       </c>
       <c r="N5" t="n">
-        <v>635.1310621415944</v>
+        <v>632.741764982106</v>
       </c>
       <c r="O5" t="n">
-        <v>25.20180672375682</v>
+        <v>25.15435876706274</v>
       </c>
       <c r="P5" t="n">
-        <v>329.3922552568645</v>
+        <v>329.3327721674719</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37446,28 +37593,28 @@
         <v>0.0738</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.729967283609394</v>
+        <v>-0.7222861660757849</v>
       </c>
       <c r="J6" t="n">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="K6" t="n">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04116743650622823</v>
+        <v>0.04066339178537559</v>
       </c>
       <c r="M6" t="n">
-        <v>23.09775476081858</v>
+        <v>23.04221719378349</v>
       </c>
       <c r="N6" t="n">
-        <v>702.8730516371888</v>
+        <v>700.372911105719</v>
       </c>
       <c r="O6" t="n">
-        <v>26.51175308494685</v>
+        <v>26.4645595297885</v>
       </c>
       <c r="P6" t="n">
-        <v>324.7577244862512</v>
+        <v>324.6795576895271</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37524,28 +37671,28 @@
         <v>0.07820000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5617575069451194</v>
+        <v>-0.5569507234356932</v>
       </c>
       <c r="J7" t="n">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="K7" t="n">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0496524514149943</v>
+        <v>0.04924034666860688</v>
       </c>
       <c r="M7" t="n">
-        <v>15.96583444525203</v>
+        <v>15.92400653103014</v>
       </c>
       <c r="N7" t="n">
-        <v>342.0744862472249</v>
+        <v>340.8211333957403</v>
       </c>
       <c r="O7" t="n">
-        <v>18.49525577674515</v>
+        <v>18.46134159252085</v>
       </c>
       <c r="P7" t="n">
-        <v>333.7395869208502</v>
+        <v>333.6906698341343</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37602,28 +37749,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4556071884198095</v>
+        <v>-0.4512962769490443</v>
       </c>
       <c r="J8" t="n">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="K8" t="n">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0268817523192959</v>
+        <v>0.02661006453048431</v>
       </c>
       <c r="M8" t="n">
-        <v>17.83462340797052</v>
+        <v>17.7830136666065</v>
       </c>
       <c r="N8" t="n">
-        <v>425.5693348452349</v>
+        <v>423.9432794477236</v>
       </c>
       <c r="O8" t="n">
-        <v>20.62933190496568</v>
+        <v>20.58988293914571</v>
       </c>
       <c r="P8" t="n">
-        <v>328.5436190008606</v>
+        <v>328.4997469182308</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37680,28 +37827,28 @@
         <v>0.06270000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3945794381285208</v>
+        <v>-0.3910249709250783</v>
       </c>
       <c r="J9" t="n">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="K9" t="n">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0180278793983929</v>
+        <v>0.01786214764033311</v>
       </c>
       <c r="M9" t="n">
-        <v>18.93940981928169</v>
+        <v>18.87914996136737</v>
       </c>
       <c r="N9" t="n">
-        <v>480.2911276168303</v>
+        <v>478.3999100124183</v>
       </c>
       <c r="O9" t="n">
-        <v>21.91554534153395</v>
+        <v>21.87235492608005</v>
       </c>
       <c r="P9" t="n">
-        <v>327.047071836488</v>
+        <v>327.0108966502332</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37758,28 +37905,28 @@
         <v>0.0471</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4204811221049798</v>
+        <v>-0.4178144530228989</v>
       </c>
       <c r="J10" t="n">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="K10" t="n">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01398357541749951</v>
+        <v>0.01392870468368634</v>
       </c>
       <c r="M10" t="n">
-        <v>23.11449685111943</v>
+        <v>23.03216532123492</v>
       </c>
       <c r="N10" t="n">
-        <v>718.2995232774402</v>
+        <v>715.3770906215989</v>
       </c>
       <c r="O10" t="n">
-        <v>26.8011104859004</v>
+        <v>26.74653417962034</v>
       </c>
       <c r="P10" t="n">
-        <v>327.6756649686168</v>
+        <v>327.6487839915134</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37817,7 +37964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K727"/>
+  <dimension ref="A1:K730"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79179,6 +79326,177 @@
         </is>
       </c>
     </row>
+    <row r="728">
+      <c r="A728" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:07:53+00:00</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>-43.048663158592866,173.07189908508028</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>-43.04849393033534,173.07102953217557</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>-43.048320781463914,173.07014514358647</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>-43.04829329001433,173.0692127442352</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>-43.048233089025445,173.068296030374</t>
+        </is>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>-43.048315160944966,173.0673822970387</t>
+        </is>
+      </c>
+      <c r="H728" t="inlineStr">
+        <is>
+          <t>-43.048318937190295,173.0664730582073</t>
+        </is>
+      </c>
+      <c r="I728" t="inlineStr">
+        <is>
+          <t>-43.048343467039956,173.06557532331223</t>
+        </is>
+      </c>
+      <c r="J728" t="inlineStr">
+        <is>
+          <t>-43.048359631674074,173.0646770458062</t>
+        </is>
+      </c>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:14:06+00:00</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>-43.04867533186753,173.07189567916447</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>-43.04851439552236,173.07102380610954</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>-43.04834919002828,173.07013855953355</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>-43.04832191101769,173.06920939870392</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>-43.04827080268244,173.0682944708866</t>
+        </is>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>-43.0483413636519,173.06738272445796</t>
+        </is>
+      </c>
+      <c r="H729" t="inlineStr">
+        <is>
+          <t>-43.048343313173206,173.06647464020077</t>
+        </is>
+      </c>
+      <c r="I729" t="inlineStr">
+        <is>
+          <t>-43.04836676365165,173.06557683502623</t>
+        </is>
+      </c>
+      <c r="J729" t="inlineStr">
+        <is>
+          <t>-43.04838778550425,173.0646788724279</t>
+        </is>
+      </c>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:07:44+00:00</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>-43.048679742474256,173.07189444513668</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>-43.04851960003105,173.07102234991112</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>-43.04835868914187,173.07013635798947</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>-43.04833187005015,173.06920823458418</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>-43.04828457401772,173.0682939014313</t>
+        </is>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>-43.04834937753819,173.06738285518077</t>
+        </is>
+      </c>
+      <c r="H730" t="inlineStr">
+        <is>
+          <t>-43.04835518634566,173.06647541076632</t>
+        </is>
+      </c>
+      <c r="I730" t="inlineStr">
+        <is>
+          <t>-43.04837719765533,173.0655775120877</t>
+        </is>
+      </c>
+      <c r="J730" t="inlineStr">
+        <is>
+          <t>-43.048401727496746,173.0646797769856</t>
+        </is>
+      </c>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0416/nzd0416.xlsx
+++ b/data/nzd0416/nzd0416.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K730"/>
+  <dimension ref="A1:K733"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28876,6 +28876,123 @@
       <c r="K730" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-25 22:07:43+00:00</t>
+        </is>
+      </c>
+      <c r="B731" t="n">
+        <v>323.25</v>
+      </c>
+      <c r="C731" t="n">
+        <v>321.9</v>
+      </c>
+      <c r="D731" t="n">
+        <v>321.99</v>
+      </c>
+      <c r="E731" t="n">
+        <v>329.03</v>
+      </c>
+      <c r="F731" t="n">
+        <v>329.15</v>
+      </c>
+      <c r="G731" t="n">
+        <v>335.62</v>
+      </c>
+      <c r="H731" t="n">
+        <v>331.29</v>
+      </c>
+      <c r="I731" t="n">
+        <v>330.22</v>
+      </c>
+      <c r="J731" t="n">
+        <v>331</v>
+      </c>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B732" t="n">
+        <v>324.39</v>
+      </c>
+      <c r="C732" t="n">
+        <v>323.86</v>
+      </c>
+      <c r="D732" t="n">
+        <v>327.01</v>
+      </c>
+      <c r="E732" t="n">
+        <v>333.38</v>
+      </c>
+      <c r="F732" t="n">
+        <v>334.37</v>
+      </c>
+      <c r="G732" t="n">
+        <v>339.36</v>
+      </c>
+      <c r="H732" t="n">
+        <v>334.95</v>
+      </c>
+      <c r="I732" t="n">
+        <v>333.92</v>
+      </c>
+      <c r="J732" t="n">
+        <v>336.08</v>
+      </c>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:07:46+00:00</t>
+        </is>
+      </c>
+      <c r="B733" t="n">
+        <v>323.59</v>
+      </c>
+      <c r="C733" t="n">
+        <v>323.63</v>
+      </c>
+      <c r="D733" t="n">
+        <v>327.19</v>
+      </c>
+      <c r="E733" t="n">
+        <v>333.44</v>
+      </c>
+      <c r="F733" t="n">
+        <v>334.15</v>
+      </c>
+      <c r="G733" t="n">
+        <v>339.13</v>
+      </c>
+      <c r="H733" t="n">
+        <v>334.89</v>
+      </c>
+      <c r="I733" t="n">
+        <v>334.22</v>
+      </c>
+      <c r="J733" t="n">
+        <v>336.58</v>
+      </c>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -28890,7 +29007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B822"/>
+  <dimension ref="A1:B825"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37113,6 +37230,36 @@
       </c>
       <c r="B822" t="n">
         <v>0.83</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>2026-01-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B823" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B824" t="n">
+        <v>-0.87</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B825" t="n">
+        <v>-0.46</v>
       </c>
     </row>
   </sheetData>
@@ -37281,28 +37428,28 @@
         <v>0.0689</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6197350095727854</v>
+        <v>-0.6129986380042519</v>
       </c>
       <c r="J2" t="n">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="K2" t="n">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08289597662606252</v>
+        <v>0.08182012243400305</v>
       </c>
       <c r="M2" t="n">
-        <v>13.33820245973358</v>
+        <v>13.32111069871827</v>
       </c>
       <c r="N2" t="n">
-        <v>243.858739222552</v>
+        <v>243.1549580964993</v>
       </c>
       <c r="O2" t="n">
-        <v>15.61597704988554</v>
+        <v>15.593426759263</v>
       </c>
       <c r="P2" t="n">
-        <v>331.5988294466263</v>
+        <v>331.530464799653</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -37359,28 +37506,28 @@
         <v>0.07149999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.7898085912008009</v>
+        <v>-0.7818809617339401</v>
       </c>
       <c r="J3" t="n">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="K3" t="n">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07479321391993765</v>
+        <v>0.07394862936054114</v>
       </c>
       <c r="M3" t="n">
-        <v>17.45449998165669</v>
+        <v>17.42500872242165</v>
       </c>
       <c r="N3" t="n">
-        <v>442.8548828424173</v>
+        <v>441.4511899330506</v>
       </c>
       <c r="O3" t="n">
-        <v>21.04411753536882</v>
+        <v>21.01073987114805</v>
       </c>
       <c r="P3" t="n">
-        <v>333.9714913303508</v>
+        <v>333.8910316561392</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37437,28 +37584,28 @@
         <v>0.06660000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6286019407772983</v>
+        <v>-0.6133834593536494</v>
       </c>
       <c r="J4" t="n">
+        <v>732</v>
+      </c>
+      <c r="K4" t="n">
         <v>729</v>
       </c>
-      <c r="K4" t="n">
-        <v>726</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.02517825179811206</v>
+        <v>0.02417031175895279</v>
       </c>
       <c r="M4" t="n">
-        <v>25.63090543761761</v>
+        <v>25.60370864726906</v>
       </c>
       <c r="N4" t="n">
-        <v>870.6530359053527</v>
+        <v>868.5804047048923</v>
       </c>
       <c r="O4" t="n">
-        <v>29.506830326305</v>
+        <v>29.47168818891942</v>
       </c>
       <c r="P4" t="n">
-        <v>322.893105700974</v>
+        <v>322.7375597571207</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37515,28 +37662,28 @@
         <v>0.07149999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.696940346848784</v>
+        <v>-0.6802013211897464</v>
       </c>
       <c r="J5" t="n">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="K5" t="n">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04185425517086949</v>
+        <v>0.04017784042397654</v>
       </c>
       <c r="M5" t="n">
-        <v>21.85701635525201</v>
+        <v>21.85162215047052</v>
       </c>
       <c r="N5" t="n">
-        <v>632.741764982106</v>
+        <v>631.9563051977552</v>
       </c>
       <c r="O5" t="n">
-        <v>25.15435876706274</v>
+        <v>25.13874112197656</v>
       </c>
       <c r="P5" t="n">
-        <v>329.3327721674719</v>
+        <v>329.1617692260114</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37593,28 +37740,28 @@
         <v>0.0738</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7222861660757849</v>
+        <v>-0.7008313066798392</v>
       </c>
       <c r="J6" t="n">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="K6" t="n">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04066339178537559</v>
+        <v>0.03854547030205369</v>
       </c>
       <c r="M6" t="n">
-        <v>23.04221719378349</v>
+        <v>23.05753284967264</v>
       </c>
       <c r="N6" t="n">
-        <v>700.372911105719</v>
+        <v>700.4712498400264</v>
       </c>
       <c r="O6" t="n">
-        <v>26.4645595297885</v>
+        <v>26.4664173971474</v>
       </c>
       <c r="P6" t="n">
-        <v>324.6795576895271</v>
+        <v>324.4603812802648</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37671,28 +37818,28 @@
         <v>0.07820000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5569507234356932</v>
+        <v>-0.5417810588566148</v>
       </c>
       <c r="J7" t="n">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="K7" t="n">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04924034666860688</v>
+        <v>0.0469188535620646</v>
       </c>
       <c r="M7" t="n">
-        <v>15.92400653103014</v>
+        <v>15.93360189315313</v>
       </c>
       <c r="N7" t="n">
-        <v>340.8211333957403</v>
+        <v>340.9086714353575</v>
       </c>
       <c r="O7" t="n">
-        <v>18.46134159252085</v>
+        <v>18.46371228749402</v>
       </c>
       <c r="P7" t="n">
-        <v>333.6906698341343</v>
+        <v>333.5357012538182</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37749,28 +37896,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4512962769490443</v>
+        <v>-0.4376596922005069</v>
       </c>
       <c r="J8" t="n">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="K8" t="n">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02661006453048431</v>
+        <v>0.0252135284058117</v>
       </c>
       <c r="M8" t="n">
-        <v>17.7830136666065</v>
+        <v>17.77910932544038</v>
       </c>
       <c r="N8" t="n">
-        <v>423.9432794477236</v>
+        <v>423.4058898897399</v>
       </c>
       <c r="O8" t="n">
-        <v>20.58988293914571</v>
+        <v>20.57682895612781</v>
       </c>
       <c r="P8" t="n">
-        <v>328.4997469182308</v>
+        <v>328.3604380805978</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37827,28 +37974,28 @@
         <v>0.06270000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3910249709250783</v>
+        <v>-0.3782077576439482</v>
       </c>
       <c r="J9" t="n">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="K9" t="n">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01786214764033311</v>
+        <v>0.01683910253357113</v>
       </c>
       <c r="M9" t="n">
-        <v>18.87914996136737</v>
+        <v>18.86533348085071</v>
       </c>
       <c r="N9" t="n">
-        <v>478.3999100124183</v>
+        <v>477.5011781654662</v>
       </c>
       <c r="O9" t="n">
-        <v>21.87235492608005</v>
+        <v>21.85180034151571</v>
       </c>
       <c r="P9" t="n">
-        <v>327.0108966502332</v>
+        <v>326.8799558113089</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37905,28 +38052,28 @@
         <v>0.0471</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4178144530228989</v>
+        <v>-0.4036561585683855</v>
       </c>
       <c r="J10" t="n">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="K10" t="n">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01392870468368634</v>
+        <v>0.01310207826497234</v>
       </c>
       <c r="M10" t="n">
-        <v>23.03216532123492</v>
+        <v>23.00895162660061</v>
       </c>
       <c r="N10" t="n">
-        <v>715.3770906215989</v>
+        <v>713.759765591685</v>
       </c>
       <c r="O10" t="n">
-        <v>26.74653417962034</v>
+        <v>26.71628278020138</v>
       </c>
       <c r="P10" t="n">
-        <v>327.6487839915134</v>
+        <v>327.5055337833356</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37964,7 +38111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K730"/>
+  <dimension ref="A1:K733"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79497,6 +79644,177 @@
         </is>
       </c>
     </row>
+    <row r="731">
+      <c r="A731" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-25 22:07:43+00:00</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>-43.04871670335801,173.07188410397683</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>-43.04857261544893,173.07100751641823</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>-43.048439919877275,173.0701175316739</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>-43.04841306756594,173.0691987433236</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>-43.04838907414912,173.06828958026233</t>
+        </is>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>-43.04843140731741,173.06738419325558</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr">
+        <is>
+          <t>-43.04842336713835,173.0664798356864</t>
+        </is>
+      </c>
+      <c r="I731" t="inlineStr">
+        <is>
+          <t>-43.04844456893703,173.06558188380924</t>
+        </is>
+      </c>
+      <c r="J731" t="inlineStr">
+        <is>
+          <t>-43.04848241115578,173.06468501175658</t>
+        </is>
+      </c>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>-43.04872675954099,173.07188129038943</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>-43.04858990500233,173.07100267886761</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>-43.04848448580899,173.07010720289827</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>-43.04845209620544,173.06919418121714</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>-43.04843605870365,173.06828763740646</t>
+        </is>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>-43.04846508364794,173.06738474258702</t>
+        </is>
+      </c>
+      <c r="H732" t="inlineStr">
+        <is>
+          <t>-43.048456288206765,173.06648197226087</t>
+        </is>
+      </c>
+      <c r="I732" t="inlineStr">
+        <is>
+          <t>-43.04847784981015,173.06558404340822</t>
+        </is>
+      </c>
+      <c r="J732" t="inlineStr">
+        <is>
+          <t>-43.048528104910794,173.0646879763822</t>
+        </is>
+      </c>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:07:46+00:00</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>-43.048719702570494,173.07188326483683</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>-43.048587876126184,173.0710032465395</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>-43.0484860837906,173.07010683254347</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>-43.04845263453149,173.06919411829148</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>-43.04843407851171,173.06828771928932</t>
+        </is>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>-43.04846301264366,173.06738470880458</t>
+        </is>
+      </c>
+      <c r="H733" t="inlineStr">
+        <is>
+          <t>-43.04845574851713,173.06648193723504</t>
+        </is>
+      </c>
+      <c r="I733" t="inlineStr">
+        <is>
+          <t>-43.04848054825931,173.06558421851093</t>
+        </is>
+      </c>
+      <c r="J733" t="inlineStr">
+        <is>
+          <t>-43.0485326023276,173.06468826817633</t>
+        </is>
+      </c>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0416/nzd0416.xlsx
+++ b/data/nzd0416/nzd0416.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K733"/>
+  <dimension ref="A1:K737"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28991,6 +28991,162 @@
         <v>336.58</v>
       </c>
       <c r="K733" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:13:43+00:00</t>
+        </is>
+      </c>
+      <c r="B734" t="n">
+        <v>324.45</v>
+      </c>
+      <c r="C734" t="n">
+        <v>325.56</v>
+      </c>
+      <c r="D734" t="n">
+        <v>333.15</v>
+      </c>
+      <c r="E734" t="n">
+        <v>339.32</v>
+      </c>
+      <c r="F734" t="n">
+        <v>340.85</v>
+      </c>
+      <c r="G734" t="n">
+        <v>341.54</v>
+      </c>
+      <c r="H734" t="n">
+        <v>339.94</v>
+      </c>
+      <c r="I734" t="n">
+        <v>339.31</v>
+      </c>
+      <c r="J734" t="n">
+        <v>343.34</v>
+      </c>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:07:43+00:00</t>
+        </is>
+      </c>
+      <c r="B735" t="n">
+        <v>324</v>
+      </c>
+      <c r="C735" t="n">
+        <v>324.69</v>
+      </c>
+      <c r="D735" t="n">
+        <v>332.6</v>
+      </c>
+      <c r="E735" t="n">
+        <v>338.9</v>
+      </c>
+      <c r="F735" t="n">
+        <v>340.57</v>
+      </c>
+      <c r="G735" t="n">
+        <v>341.3</v>
+      </c>
+      <c r="H735" t="n">
+        <v>339.59</v>
+      </c>
+      <c r="I735" t="n">
+        <v>338.85</v>
+      </c>
+      <c r="J735" t="n">
+        <v>342.81</v>
+      </c>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:13:48+00:00</t>
+        </is>
+      </c>
+      <c r="B736" t="n">
+        <v>323.9</v>
+      </c>
+      <c r="C736" t="n">
+        <v>325.4</v>
+      </c>
+      <c r="D736" t="n">
+        <v>332.73</v>
+      </c>
+      <c r="E736" t="n">
+        <v>339.22</v>
+      </c>
+      <c r="F736" t="n">
+        <v>340.42</v>
+      </c>
+      <c r="G736" t="n">
+        <v>341.57</v>
+      </c>
+      <c r="H736" t="n">
+        <v>340.98</v>
+      </c>
+      <c r="I736" t="n">
+        <v>339.87</v>
+      </c>
+      <c r="J736" t="n">
+        <v>345.18</v>
+      </c>
+      <c r="K736" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:07:33+00:00</t>
+        </is>
+      </c>
+      <c r="B737" t="n">
+        <v>325.59</v>
+      </c>
+      <c r="C737" t="n">
+        <v>322.99</v>
+      </c>
+      <c r="D737" t="n">
+        <v>329.86</v>
+      </c>
+      <c r="E737" t="n">
+        <v>337.37</v>
+      </c>
+      <c r="F737" t="n">
+        <v>339.46</v>
+      </c>
+      <c r="G737" t="n">
+        <v>340.76</v>
+      </c>
+      <c r="H737" t="n">
+        <v>339.8</v>
+      </c>
+      <c r="I737" t="n">
+        <v>338.44</v>
+      </c>
+      <c r="J737" t="n">
+        <v>343.23</v>
+      </c>
+      <c r="K737" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29007,7 +29163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B825"/>
+  <dimension ref="A1:B829"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37260,6 +37416,46 @@
       </c>
       <c r="B825" t="n">
         <v>-0.46</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B826" t="n">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B827" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B828" t="n">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B829" t="n">
+        <v>0.31</v>
       </c>
     </row>
   </sheetData>
@@ -37428,28 +37624,28 @@
         <v>0.0689</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6129986380042519</v>
+        <v>-0.6033745198791138</v>
       </c>
       <c r="J2" t="n">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="K2" t="n">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08182012243400305</v>
+        <v>0.08019860039654558</v>
       </c>
       <c r="M2" t="n">
-        <v>13.32111069871827</v>
+        <v>13.30218173751784</v>
       </c>
       <c r="N2" t="n">
-        <v>243.1549580964993</v>
+        <v>242.2904057266951</v>
       </c>
       <c r="O2" t="n">
-        <v>15.593426759263</v>
+        <v>15.56568038110429</v>
       </c>
       <c r="P2" t="n">
-        <v>331.530464799653</v>
+        <v>331.4323600449719</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -37506,28 +37702,28 @@
         <v>0.07149999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.7818809617339401</v>
+        <v>-0.7698629863835492</v>
       </c>
       <c r="J3" t="n">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="K3" t="n">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07394862936054114</v>
+        <v>0.07253340708301592</v>
       </c>
       <c r="M3" t="n">
-        <v>17.42500872242165</v>
+        <v>17.39315641493825</v>
       </c>
       <c r="N3" t="n">
-        <v>441.4511899330506</v>
+        <v>439.7664415221737</v>
       </c>
       <c r="O3" t="n">
-        <v>21.01073987114805</v>
+        <v>20.97060899263953</v>
       </c>
       <c r="P3" t="n">
-        <v>333.8910316561392</v>
+        <v>333.7685379482232</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37584,28 +37780,28 @@
         <v>0.06660000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6133834593536494</v>
+        <v>-0.5864400825447511</v>
       </c>
       <c r="J4" t="n">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="K4" t="n">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02417031175895279</v>
+        <v>0.02230712375570632</v>
       </c>
       <c r="M4" t="n">
-        <v>25.60370864726906</v>
+        <v>25.60067974246576</v>
       </c>
       <c r="N4" t="n">
-        <v>868.5804047048923</v>
+        <v>867.3717143123287</v>
       </c>
       <c r="O4" t="n">
-        <v>29.47168818891942</v>
+        <v>29.4511750922154</v>
       </c>
       <c r="P4" t="n">
-        <v>322.7375597571207</v>
+        <v>322.4610151829434</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37662,28 +37858,28 @@
         <v>0.07149999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6802013211897464</v>
+        <v>-0.6511944870690736</v>
       </c>
       <c r="J5" t="n">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="K5" t="n">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04017784042397654</v>
+        <v>0.03713799650476146</v>
       </c>
       <c r="M5" t="n">
-        <v>21.85162215047052</v>
+        <v>21.87785240577593</v>
       </c>
       <c r="N5" t="n">
-        <v>631.9563051977552</v>
+        <v>632.5951057479904</v>
       </c>
       <c r="O5" t="n">
-        <v>25.13874112197656</v>
+        <v>25.15144341281411</v>
       </c>
       <c r="P5" t="n">
-        <v>329.1617692260114</v>
+        <v>328.8641802551238</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37740,28 +37936,28 @@
         <v>0.0738</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7008313066798392</v>
+        <v>-0.6646032133796848</v>
       </c>
       <c r="J6" t="n">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="K6" t="n">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03854547030205369</v>
+        <v>0.03488943754531293</v>
       </c>
       <c r="M6" t="n">
-        <v>23.05753284967264</v>
+        <v>23.11538027788271</v>
       </c>
       <c r="N6" t="n">
-        <v>700.4712498400264</v>
+        <v>703.0185641022374</v>
       </c>
       <c r="O6" t="n">
-        <v>26.4664173971474</v>
+        <v>26.5144972440029</v>
       </c>
       <c r="P6" t="n">
-        <v>324.4603812802648</v>
+        <v>324.0887043588074</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37818,28 +38014,28 @@
         <v>0.07820000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5417810588566148</v>
+        <v>-0.5185122908429723</v>
       </c>
       <c r="J7" t="n">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="K7" t="n">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0469188535620646</v>
+        <v>0.04331429632583683</v>
       </c>
       <c r="M7" t="n">
-        <v>15.93360189315313</v>
+        <v>15.96031881909579</v>
       </c>
       <c r="N7" t="n">
-        <v>340.9086714353575</v>
+        <v>341.676374956126</v>
       </c>
       <c r="O7" t="n">
-        <v>18.46371228749402</v>
+        <v>18.4844901189112</v>
       </c>
       <c r="P7" t="n">
-        <v>333.5357012538182</v>
+        <v>333.296977981592</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37896,28 +38092,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4376596922005069</v>
+        <v>-0.4131337945809203</v>
       </c>
       <c r="J8" t="n">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="K8" t="n">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0252135284058117</v>
+        <v>0.02263673644633957</v>
       </c>
       <c r="M8" t="n">
-        <v>17.77910932544038</v>
+        <v>17.80649056352716</v>
       </c>
       <c r="N8" t="n">
-        <v>423.4058898897399</v>
+        <v>424.0162098754551</v>
       </c>
       <c r="O8" t="n">
-        <v>20.57682895612781</v>
+        <v>20.59165388878356</v>
       </c>
       <c r="P8" t="n">
-        <v>328.3604380805978</v>
+        <v>328.1088143876815</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37974,28 +38170,28 @@
         <v>0.06270000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3782077576439482</v>
+        <v>-0.3547906916419067</v>
       </c>
       <c r="J9" t="n">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="K9" t="n">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01683910253357113</v>
+        <v>0.01493960243239756</v>
       </c>
       <c r="M9" t="n">
-        <v>18.86533348085071</v>
+        <v>18.87739151234325</v>
       </c>
       <c r="N9" t="n">
-        <v>477.5011781654662</v>
+        <v>477.5590422127262</v>
       </c>
       <c r="O9" t="n">
-        <v>21.85180034151571</v>
+        <v>21.85312431238898</v>
       </c>
       <c r="P9" t="n">
-        <v>326.8799558113089</v>
+        <v>326.6397107756923</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -38052,28 +38248,28 @@
         <v>0.0471</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4036561585683855</v>
+        <v>-0.3756730778957141</v>
       </c>
       <c r="J10" t="n">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="K10" t="n">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01310207826497234</v>
+        <v>0.01143887747906647</v>
       </c>
       <c r="M10" t="n">
-        <v>23.00895162660061</v>
+        <v>23.0241914580046</v>
       </c>
       <c r="N10" t="n">
-        <v>713.759765591685</v>
+        <v>713.735178679397</v>
       </c>
       <c r="O10" t="n">
-        <v>26.71628278020138</v>
+        <v>26.7158226277874</v>
       </c>
       <c r="P10" t="n">
-        <v>327.5055337833356</v>
+        <v>327.2211813185436</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -38111,7 +38307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K733"/>
+  <dimension ref="A1:K737"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79815,6 +80011,234 @@
         </is>
       </c>
     </row>
+    <row r="734">
+      <c r="A734" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:13:43+00:00</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>-43.04872728881377,173.07188114230587</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>-43.04860490104334,173.07099848303068</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>-43.048538994735715,173.07009456967435</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>-43.04850539048487,173.06918795157276</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>-43.04849438435697,173.06828522558132</t>
+        </is>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>-43.04848471316671,173.06738506278586</t>
+        </is>
+      </c>
+      <c r="H734" t="inlineStr">
+        <is>
+          <t>-43.04850117239529,173.06648488524448</t>
+        </is>
+      </c>
+      <c r="I734" t="inlineStr">
+        <is>
+          <t>-43.04852633194651,173.06558718942284</t>
+        </is>
+      </c>
+      <c r="J734" t="inlineStr">
+        <is>
+          <t>-43.048593407402414,173.06469221323678</t>
+        </is>
+      </c>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:07:43+00:00</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>-43.048723319267864,173.0718822529326</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>-43.048597226598844,173.0710006303122</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>-43.04853411201435,173.07009570131584</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>-43.048501622202515,173.06918839205304</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>-43.04849186411271,173.06828532979608</t>
+        </is>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>-43.04848255211877,173.0673850275346</t>
+        </is>
+      </c>
+      <c r="H735" t="inlineStr">
+        <is>
+          <t>-43.04849802420573,173.06648468092686</t>
+        </is>
+      </c>
+      <c r="I735" t="inlineStr">
+        <is>
+          <t>-43.0485221943245,173.0655869209316</t>
+        </is>
+      </c>
+      <c r="J735" t="inlineStr">
+        <is>
+          <t>-43.048588640140665,173.0646919039344</t>
+        </is>
+      </c>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:13:48+00:00</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>-43.048722437146566,173.07188249973854</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>-43.04860348965125,173.07099887793308</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>-43.04853526611212,173.07009543383697</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>-43.0485044932748,173.06918805644904</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>-43.04849051398185,173.0682853856254</t>
+        </is>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>-43.048484983297705,173.06738506719225</t>
+        </is>
+      </c>
+      <c r="H736" t="inlineStr">
+        <is>
+          <t>-43.0485105270157,173.06648549235985</t>
+        </is>
+      </c>
+      <c r="I736" t="inlineStr">
+        <is>
+          <t>-43.04853136905155,173.0655875162818</t>
+        </is>
+      </c>
+      <c r="J736" t="inlineStr">
+        <is>
+          <t>-43.048609957896005,173.06469328704156</t>
+        </is>
+      </c>
+      <c r="K736" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:07:33+00:00</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>-43.048737344996646,173.07187832871753</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>-43.048582230557734,173.07100482614806</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>-43.04850978718401,173.0701013389453</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>-43.04848789488819,173.06918999665922</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>-43.04848187314435,173.06828574293306</t>
+        </is>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>-43.04847768976092,173.06738494821928</t>
+        </is>
+      </c>
+      <c r="H737" t="inlineStr">
+        <is>
+          <t>-43.048499913119464,173.06648480351743</t>
+        </is>
+      </c>
+      <c r="I737" t="inlineStr">
+        <is>
+          <t>-43.048518506444005,173.0655866816242</t>
+        </is>
+      </c>
+      <c r="J737" t="inlineStr">
+        <is>
+          <t>-43.04859241797074,173.06469214904195</t>
+        </is>
+      </c>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0416/nzd0416.xlsx
+++ b/data/nzd0416/nzd0416.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K737"/>
+  <dimension ref="A1:K741"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29147,6 +29147,162 @@
         <v>343.23</v>
       </c>
       <c r="K737" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:07:26+00:00</t>
+        </is>
+      </c>
+      <c r="B738" t="n">
+        <v>323.54</v>
+      </c>
+      <c r="C738" t="n">
+        <v>320.89</v>
+      </c>
+      <c r="D738" t="n">
+        <v>326.01</v>
+      </c>
+      <c r="E738" t="n">
+        <v>333.99</v>
+      </c>
+      <c r="F738" t="n">
+        <v>335.46</v>
+      </c>
+      <c r="G738" t="n">
+        <v>338.62</v>
+      </c>
+      <c r="H738" t="n">
+        <v>336.99</v>
+      </c>
+      <c r="I738" t="n">
+        <v>335.34</v>
+      </c>
+      <c r="J738" t="n">
+        <v>340.03</v>
+      </c>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:13:35+00:00</t>
+        </is>
+      </c>
+      <c r="B739" t="n">
+        <v>321.87</v>
+      </c>
+      <c r="C739" t="n">
+        <v>318.48</v>
+      </c>
+      <c r="D739" t="n">
+        <v>321.91</v>
+      </c>
+      <c r="E739" t="n">
+        <v>330.08</v>
+      </c>
+      <c r="F739" t="n">
+        <v>331.2</v>
+      </c>
+      <c r="G739" t="n">
+        <v>335.53</v>
+      </c>
+      <c r="H739" t="n">
+        <v>333.56</v>
+      </c>
+      <c r="I739" t="n">
+        <v>331.9</v>
+      </c>
+      <c r="J739" t="n">
+        <v>335.74</v>
+      </c>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:07:11+00:00</t>
+        </is>
+      </c>
+      <c r="B740" t="n">
+        <v>320.03</v>
+      </c>
+      <c r="C740" t="n">
+        <v>316.17</v>
+      </c>
+      <c r="D740" t="n">
+        <v>318</v>
+      </c>
+      <c r="E740" t="n">
+        <v>326.26</v>
+      </c>
+      <c r="F740" t="n">
+        <v>327.18</v>
+      </c>
+      <c r="G740" t="n">
+        <v>333.03</v>
+      </c>
+      <c r="H740" t="n">
+        <v>330.13</v>
+      </c>
+      <c r="I740" t="n">
+        <v>328.34</v>
+      </c>
+      <c r="J740" t="n">
+        <v>331.61</v>
+      </c>
+      <c r="K740" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:07:22+00:00</t>
+        </is>
+      </c>
+      <c r="B741" t="n">
+        <v>318.4</v>
+      </c>
+      <c r="C741" t="n">
+        <v>313.32</v>
+      </c>
+      <c r="D741" t="n">
+        <v>314.43</v>
+      </c>
+      <c r="E741" t="n">
+        <v>322.88</v>
+      </c>
+      <c r="F741" t="n">
+        <v>323.48</v>
+      </c>
+      <c r="G741" t="n">
+        <v>330.26</v>
+      </c>
+      <c r="H741" t="n">
+        <v>327.44</v>
+      </c>
+      <c r="I741" t="n">
+        <v>325.5</v>
+      </c>
+      <c r="J741" t="n">
+        <v>328.74</v>
+      </c>
+      <c r="K741" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29163,7 +29319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B829"/>
+  <dimension ref="A1:B833"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37456,6 +37612,46 @@
       </c>
       <c r="B829" t="n">
         <v>0.31</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B830" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B831" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B832" t="n">
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B833" t="n">
+        <v>0.71</v>
       </c>
     </row>
   </sheetData>
@@ -37624,28 +37820,28 @@
         <v>0.0689</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6033745198791138</v>
+        <v>-0.5975846994876779</v>
       </c>
       <c r="J2" t="n">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="K2" t="n">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08019860039654558</v>
+        <v>0.07958324689855389</v>
       </c>
       <c r="M2" t="n">
-        <v>13.30218173751784</v>
+        <v>13.26212391869239</v>
       </c>
       <c r="N2" t="n">
-        <v>242.2904057266951</v>
+        <v>241.1673528550377</v>
       </c>
       <c r="O2" t="n">
-        <v>15.56568038110429</v>
+        <v>15.52956383338044</v>
       </c>
       <c r="P2" t="n">
-        <v>331.4323600449719</v>
+        <v>331.3731056260574</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -37702,28 +37898,28 @@
         <v>0.07149999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.7698629863835492</v>
+        <v>-0.7657798208474313</v>
       </c>
       <c r="J3" t="n">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="K3" t="n">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07253340708301592</v>
+        <v>0.07258493506364561</v>
       </c>
       <c r="M3" t="n">
-        <v>17.39315641493825</v>
+        <v>17.32027772917283</v>
       </c>
       <c r="N3" t="n">
-        <v>439.7664415221737</v>
+        <v>437.5142537303651</v>
       </c>
       <c r="O3" t="n">
-        <v>20.97060899263953</v>
+        <v>20.91684138990314</v>
       </c>
       <c r="P3" t="n">
-        <v>333.7685379482232</v>
+        <v>333.7267604349759</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37780,28 +37976,28 @@
         <v>0.06660000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5864400825447511</v>
+        <v>-0.572637766103327</v>
       </c>
       <c r="J4" t="n">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="K4" t="n">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02230712375570632</v>
+        <v>0.02151191476906722</v>
       </c>
       <c r="M4" t="n">
-        <v>25.60067974246576</v>
+        <v>25.5310396195648</v>
       </c>
       <c r="N4" t="n">
-        <v>867.3717143123287</v>
+        <v>863.7014589809462</v>
       </c>
       <c r="O4" t="n">
-        <v>29.4511750922154</v>
+        <v>29.38879818878183</v>
       </c>
       <c r="P4" t="n">
-        <v>322.4610151829434</v>
+        <v>322.3187746714877</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37858,28 +38054,28 @@
         <v>0.07149999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6511944870690736</v>
+        <v>-0.633711198851286</v>
       </c>
       <c r="J5" t="n">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="K5" t="n">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03713799650476146</v>
+        <v>0.03555403588630279</v>
       </c>
       <c r="M5" t="n">
-        <v>21.87785240577593</v>
+        <v>21.84624155807129</v>
       </c>
       <c r="N5" t="n">
-        <v>632.5951057479904</v>
+        <v>630.7605847655506</v>
       </c>
       <c r="O5" t="n">
-        <v>25.15144341281411</v>
+        <v>25.11494743704534</v>
       </c>
       <c r="P5" t="n">
-        <v>328.8641802551238</v>
+        <v>328.6840814915851</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37936,28 +38132,28 @@
         <v>0.0738</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6646032133796848</v>
+        <v>-0.6407042996400785</v>
       </c>
       <c r="J6" t="n">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="K6" t="n">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03488943754531293</v>
+        <v>0.03274445147373051</v>
       </c>
       <c r="M6" t="n">
-        <v>23.11538027788271</v>
+        <v>23.11112130549684</v>
       </c>
       <c r="N6" t="n">
-        <v>703.0185641022374</v>
+        <v>702.1203756389154</v>
       </c>
       <c r="O6" t="n">
-        <v>26.5144972440029</v>
+        <v>26.49755414446615</v>
       </c>
       <c r="P6" t="n">
-        <v>324.0887043588074</v>
+        <v>323.8425082803992</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -38014,28 +38210,28 @@
         <v>0.07820000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5185122908429723</v>
+        <v>-0.5030179052445294</v>
       </c>
       <c r="J7" t="n">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="K7" t="n">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04331429632583683</v>
+        <v>0.04118786496962223</v>
       </c>
       <c r="M7" t="n">
-        <v>15.96031881909579</v>
+        <v>15.94875932526512</v>
       </c>
       <c r="N7" t="n">
-        <v>341.676374956126</v>
+        <v>341.0546065873457</v>
       </c>
       <c r="O7" t="n">
-        <v>18.4844901189112</v>
+        <v>18.46766380967949</v>
       </c>
       <c r="P7" t="n">
-        <v>333.296977981592</v>
+        <v>333.1373631964912</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -38092,28 +38288,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4131337945809203</v>
+        <v>-0.3975857346058927</v>
       </c>
       <c r="J8" t="n">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="K8" t="n">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02263673644633957</v>
+        <v>0.02118079886914837</v>
       </c>
       <c r="M8" t="n">
-        <v>17.80649056352716</v>
+        <v>17.78786640391865</v>
       </c>
       <c r="N8" t="n">
-        <v>424.0162098754551</v>
+        <v>422.9748260423981</v>
       </c>
       <c r="O8" t="n">
-        <v>20.59165388878356</v>
+        <v>20.56635179224546</v>
       </c>
       <c r="P8" t="n">
-        <v>328.1088143876815</v>
+        <v>327.9486499118055</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -38170,28 +38366,28 @@
         <v>0.06270000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3547906916419067</v>
+        <v>-0.3411669168147061</v>
       </c>
       <c r="J9" t="n">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="K9" t="n">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01493960243239756</v>
+        <v>0.0139621745261842</v>
       </c>
       <c r="M9" t="n">
-        <v>18.87739151234325</v>
+        <v>18.84114188074212</v>
       </c>
       <c r="N9" t="n">
-        <v>477.5590422127262</v>
+        <v>475.9563483743195</v>
       </c>
       <c r="O9" t="n">
-        <v>21.85312431238898</v>
+        <v>21.81642382184393</v>
       </c>
       <c r="P9" t="n">
-        <v>326.6397107756923</v>
+        <v>326.4993728866043</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -38248,28 +38444,28 @@
         <v>0.0471</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3756730778957141</v>
+        <v>-0.3583029773106715</v>
       </c>
       <c r="J10" t="n">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="K10" t="n">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01143887747906647</v>
+        <v>0.01051338696672299</v>
       </c>
       <c r="M10" t="n">
-        <v>23.0241914580046</v>
+        <v>22.9861318300609</v>
       </c>
       <c r="N10" t="n">
-        <v>713.735178679397</v>
+        <v>711.4563696022499</v>
       </c>
       <c r="O10" t="n">
-        <v>26.7158226277874</v>
+        <v>26.67313947780145</v>
       </c>
       <c r="P10" t="n">
-        <v>327.2211813185436</v>
+        <v>327.0439404557039</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -38307,7 +38503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K737"/>
+  <dimension ref="A1:K741"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80239,6 +80435,234 @@
         </is>
       </c>
     </row>
+    <row r="738">
+      <c r="A738" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:07:26+00:00</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>-43.04871926150984,173.0718833882398</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>-43.04856370603611,173.0710100092366</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>-43.04847560813346,173.0701092604245</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>-43.04845756918704,173.069193541473</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>-43.048445869654635,173.06828723171395</t>
+        </is>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>-43.04845842041678,173.06738463389573</t>
+        </is>
+      </c>
+      <c r="H738" t="inlineStr">
+        <is>
+          <t>-43.04847463765465,173.06648316313942</t>
+        </is>
+      </c>
+      <c r="I738" t="inlineStr">
+        <is>
+          <t>-43.048490622469494,173.06558487222793</t>
+        </is>
+      </c>
+      <c r="J738" t="inlineStr">
+        <is>
+          <t>-43.048563634503466,173.06469028155678</t>
+        </is>
+      </c>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:13:35+00:00</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>-43.048704530083775,173.07188750989718</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>-43.04854244694189,173.0710159574439</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>-43.04843920966322,173.07011769627576</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>-43.04842248827207,173.06919764212603</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>-43.04840752593784,173.06828881726372</t>
+        </is>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>-43.04843059692443,173.06738418003638</t>
+        </is>
+      </c>
+      <c r="H739" t="inlineStr">
+        <is>
+          <t>-43.04844378539665,173.0664811608293</t>
+        </is>
+      </c>
+      <c r="I739" t="inlineStr">
+        <is>
+          <t>-43.04845968025242,173.06558286438363</t>
+        </is>
+      </c>
+      <c r="J739" t="inlineStr">
+        <is>
+          <t>-43.048525046667365,173.06468777796223</t>
+        </is>
+      </c>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:07:11+00:00</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>-43.04868829905127,173.07189205112226</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>-43.04852206996739,173.0710216588338</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>-43.04840449795056,173.0701257411881</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>-43.048388214845836,173.06920164838613</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>-43.048371342430165,173.06829031348494</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>-43.04840808600818,173.06738381283657</t>
+        </is>
+      </c>
+      <c r="H740" t="inlineStr">
+        <is>
+          <t>-43.04841293313847,173.06647915852122</t>
+        </is>
+      </c>
+      <c r="I740" t="inlineStr">
+        <is>
+          <t>-43.04842765865547,173.0655807865004</t>
+        </is>
+      </c>
+      <c r="J740" t="inlineStr">
+        <is>
+          <t>-43.04848789800435,173.06468536774486</t>
+        </is>
+      </c>
+      <c r="K740" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:07:22+00:00</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>-43.04867392047337,173.0718960740533</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>-43.048496929543816,173.07102869301096</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>-43.04837280464702,173.07013308653492</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>-43.0483578891438,173.06920519318848</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>-43.04833803920149,173.06829169060248</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>-43.04838314391287,173.06738340597948</t>
+        </is>
+      </c>
+      <c r="H741" t="inlineStr">
+        <is>
+          <t>-43.04838873705247,173.06647758819938</t>
+        </is>
+      </c>
+      <c r="I741" t="inlineStr">
+        <is>
+          <t>-43.04840211333639,173.06557912886478</t>
+        </is>
+      </c>
+      <c r="J741" t="inlineStr">
+        <is>
+          <t>-43.04846208283158,173.06468369284977</t>
+        </is>
+      </c>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0416/nzd0416.xlsx
+++ b/data/nzd0416/nzd0416.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K741"/>
+  <dimension ref="A1:K744"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29303,6 +29303,123 @@
         <v>328.74</v>
       </c>
       <c r="K741" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:13:30+00:00</t>
+        </is>
+      </c>
+      <c r="B742" t="n">
+        <v>315.11</v>
+      </c>
+      <c r="C742" t="n">
+        <v>308.92</v>
+      </c>
+      <c r="D742" t="n">
+        <v>308.3</v>
+      </c>
+      <c r="E742" t="n">
+        <v>317.09</v>
+      </c>
+      <c r="F742" t="n">
+        <v>316.81</v>
+      </c>
+      <c r="G742" t="n">
+        <v>325.75</v>
+      </c>
+      <c r="H742" t="n">
+        <v>322.4</v>
+      </c>
+      <c r="I742" t="n">
+        <v>320.51</v>
+      </c>
+      <c r="J742" t="n">
+        <v>322.53</v>
+      </c>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:07:10+00:00</t>
+        </is>
+      </c>
+      <c r="B743" t="n">
+        <v>314.65</v>
+      </c>
+      <c r="C743" t="n">
+        <v>308.92</v>
+      </c>
+      <c r="D743" t="n">
+        <v>306.15</v>
+      </c>
+      <c r="E743" t="n">
+        <v>315.09</v>
+      </c>
+      <c r="F743" t="n">
+        <v>314.16</v>
+      </c>
+      <c r="G743" t="n">
+        <v>325.75</v>
+      </c>
+      <c r="H743" t="n">
+        <v>320.67</v>
+      </c>
+      <c r="I743" t="n">
+        <v>319.13</v>
+      </c>
+      <c r="J743" t="n">
+        <v>320.7</v>
+      </c>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:06:56+00:00</t>
+        </is>
+      </c>
+      <c r="B744" t="n">
+        <v>313.57</v>
+      </c>
+      <c r="C744" t="n">
+        <v>306.46</v>
+      </c>
+      <c r="D744" t="n">
+        <v>302.69</v>
+      </c>
+      <c r="E744" t="n">
+        <v>311.53</v>
+      </c>
+      <c r="F744" t="n">
+        <v>309.75</v>
+      </c>
+      <c r="G744" t="n">
+        <v>322.21</v>
+      </c>
+      <c r="H744" t="n">
+        <v>317.98</v>
+      </c>
+      <c r="I744" t="n">
+        <v>316.16</v>
+      </c>
+      <c r="J744" t="n">
+        <v>317.49</v>
+      </c>
+      <c r="K744" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29319,7 +29436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B833"/>
+  <dimension ref="A1:B836"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37652,6 +37769,36 @@
       </c>
       <c r="B833" t="n">
         <v>0.71</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B834" t="n">
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B835" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B836" t="n">
+        <v>0.06</v>
       </c>
     </row>
   </sheetData>
@@ -37820,28 +37967,28 @@
         <v>0.0689</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5975846994876779</v>
+        <v>-0.5983348518196107</v>
       </c>
       <c r="J2" t="n">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="K2" t="n">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07958324689855389</v>
+        <v>0.08040705490135913</v>
       </c>
       <c r="M2" t="n">
-        <v>13.26212391869239</v>
+        <v>13.21224722274045</v>
       </c>
       <c r="N2" t="n">
-        <v>241.1673528550377</v>
+        <v>240.1989488624846</v>
       </c>
       <c r="O2" t="n">
-        <v>15.52956383338044</v>
+        <v>15.49835310161969</v>
       </c>
       <c r="P2" t="n">
-        <v>331.3731056260574</v>
+        <v>331.3808164224261</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -37898,28 +38045,28 @@
         <v>0.07149999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.7657798208474313</v>
+        <v>-0.769770275657509</v>
       </c>
       <c r="J3" t="n">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="K3" t="n">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07258493506364561</v>
+        <v>0.07386377018957258</v>
       </c>
       <c r="M3" t="n">
-        <v>17.32027772917283</v>
+        <v>17.27118913557995</v>
       </c>
       <c r="N3" t="n">
-        <v>437.5142537303651</v>
+        <v>435.8596871749703</v>
       </c>
       <c r="O3" t="n">
-        <v>20.91684138990314</v>
+        <v>20.87725286466038</v>
       </c>
       <c r="P3" t="n">
-        <v>333.7267604349759</v>
+        <v>333.7677550938099</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37976,28 +38123,28 @@
         <v>0.06660000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.572637766103327</v>
+        <v>-0.5736589088527961</v>
       </c>
       <c r="J4" t="n">
+        <v>743</v>
+      </c>
+      <c r="K4" t="n">
         <v>740</v>
       </c>
-      <c r="K4" t="n">
-        <v>737</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.02151191476906722</v>
+        <v>0.02177160124054023</v>
       </c>
       <c r="M4" t="n">
-        <v>25.5310396195648</v>
+        <v>25.43633569511018</v>
       </c>
       <c r="N4" t="n">
-        <v>863.7014589809462</v>
+        <v>860.2281533319544</v>
       </c>
       <c r="O4" t="n">
-        <v>29.38879818878183</v>
+        <v>29.3296463212899</v>
       </c>
       <c r="P4" t="n">
-        <v>322.3187746714877</v>
+        <v>322.3293586155848</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -38054,28 +38201,28 @@
         <v>0.07149999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.633711198851286</v>
+        <v>-0.6315315011154534</v>
       </c>
       <c r="J5" t="n">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="K5" t="n">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03555403588630279</v>
+        <v>0.03561457411594515</v>
       </c>
       <c r="M5" t="n">
-        <v>21.84624155807129</v>
+        <v>21.76923816623341</v>
       </c>
       <c r="N5" t="n">
-        <v>630.7605847655506</v>
+        <v>628.2595699466541</v>
       </c>
       <c r="O5" t="n">
-        <v>25.11494743704534</v>
+        <v>25.06510662148985</v>
       </c>
       <c r="P5" t="n">
-        <v>328.6840814915851</v>
+        <v>328.6615740076869</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -38132,28 +38279,28 @@
         <v>0.0738</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6407042996400785</v>
+        <v>-0.635395627388467</v>
       </c>
       <c r="J6" t="n">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="K6" t="n">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03274445147373051</v>
+        <v>0.03248517943788065</v>
       </c>
       <c r="M6" t="n">
-        <v>23.11112130549684</v>
+        <v>23.04428968202635</v>
       </c>
       <c r="N6" t="n">
-        <v>702.1203756389154</v>
+        <v>699.498830814957</v>
       </c>
       <c r="O6" t="n">
-        <v>26.49755414446615</v>
+        <v>26.44804020745123</v>
       </c>
       <c r="P6" t="n">
-        <v>323.8425082803992</v>
+        <v>323.7876637721799</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -38210,28 +38357,28 @@
         <v>0.07820000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5030179052445294</v>
+        <v>-0.4992384646706116</v>
       </c>
       <c r="J7" t="n">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="K7" t="n">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04118786496962223</v>
+        <v>0.04092578152621185</v>
       </c>
       <c r="M7" t="n">
-        <v>15.94875932526512</v>
+        <v>15.90228573372133</v>
       </c>
       <c r="N7" t="n">
-        <v>341.0546065873457</v>
+        <v>339.779760474221</v>
       </c>
       <c r="O7" t="n">
-        <v>18.46766380967949</v>
+        <v>18.43311586450378</v>
       </c>
       <c r="P7" t="n">
-        <v>333.1373631964912</v>
+        <v>333.0983121038566</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -38288,28 +38435,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3975857346058927</v>
+        <v>-0.3952446159203136</v>
       </c>
       <c r="J8" t="n">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="K8" t="n">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02118079886914837</v>
+        <v>0.02111475351176806</v>
       </c>
       <c r="M8" t="n">
-        <v>17.78786640391865</v>
+        <v>17.72746847464209</v>
       </c>
       <c r="N8" t="n">
-        <v>422.9748260423981</v>
+        <v>421.3120544941464</v>
       </c>
       <c r="O8" t="n">
-        <v>20.56635179224546</v>
+        <v>20.52588742281674</v>
       </c>
       <c r="P8" t="n">
-        <v>327.9486499118055</v>
+        <v>327.9244690074436</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -38366,28 +38513,28 @@
         <v>0.06270000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3411669168147061</v>
+        <v>-0.3402286463655925</v>
       </c>
       <c r="J9" t="n">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="K9" t="n">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0139621745261842</v>
+        <v>0.01400616909801755</v>
       </c>
       <c r="M9" t="n">
-        <v>18.84114188074212</v>
+        <v>18.77271259573754</v>
       </c>
       <c r="N9" t="n">
-        <v>475.9563483743195</v>
+        <v>474.0485034768892</v>
       </c>
       <c r="O9" t="n">
-        <v>21.81642382184393</v>
+        <v>21.77265494782134</v>
       </c>
       <c r="P9" t="n">
-        <v>326.4993728866043</v>
+        <v>326.4896927977985</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -38444,28 +38591,28 @@
         <v>0.0471</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3583029773106715</v>
+        <v>-0.3561797662030994</v>
       </c>
       <c r="J10" t="n">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="K10" t="n">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01051338696672299</v>
+        <v>0.01047936968732921</v>
       </c>
       <c r="M10" t="n">
-        <v>22.9861318300609</v>
+        <v>22.9031107429623</v>
       </c>
       <c r="N10" t="n">
-        <v>711.4563696022499</v>
+        <v>708.604641162696</v>
       </c>
       <c r="O10" t="n">
-        <v>26.67313947780145</v>
+        <v>26.61962886974001</v>
       </c>
       <c r="P10" t="n">
-        <v>327.0439404557039</v>
+        <v>327.022220568636</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -38503,7 +38650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K741"/>
+  <dimension ref="A1:K744"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80663,6 +80810,177 @@
         </is>
       </c>
     </row>
+    <row r="742">
+      <c r="A742" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:13:30+00:00</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>-43.04864489868063,173.07190419395144</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>-43.04845811625724,173.07103955278194</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>-43.04831838449127,173.07014569911567</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>-43.04830594067729,173.06921126548977</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>-43.048278003380624,173.06829417313222</t>
+        </is>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>-43.04834253421956,173.06738274355232</t>
+        </is>
+      </c>
+      <c r="H742" t="inlineStr">
+        <is>
+          <t>-43.048343403121486,173.0664746460384</t>
+        </is>
+      </c>
+      <c r="I742" t="inlineStr">
+        <is>
+          <t>-43.04835722913106,173.06557621633235</t>
+        </is>
+      </c>
+      <c r="J742" t="inlineStr">
+        <is>
+          <t>-43.048406224913656,173.06468006877847</t>
+        </is>
+      </c>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:07:10+00:00</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>-43.04864084092232,173.0719053292557</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>-43.04845811625724,173.07103955278194</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>-43.04829929748678,173.07015012277247</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>-43.0482879964745,173.06921336300078</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>-43.0482541510678,173.06829515944332</t>
+        </is>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>-43.04834253421956,173.06738274355232</t>
+        </is>
+      </c>
+      <c r="H743" t="inlineStr">
+        <is>
+          <t>-43.04832784206968,173.06647363613098</t>
+        </is>
+      </c>
+      <c r="I743" t="inlineStr">
+        <is>
+          <t>-43.048344816264574,173.0655754108632</t>
+        </is>
+      </c>
+      <c r="J743" t="inlineStr">
+        <is>
+          <t>-43.04838976436769,173.06467900081668</t>
+        </is>
+      </c>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:06:56+00:00</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>-43.048631314011445,173.07190799475217</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>-43.048436416101005,173.07104562437522</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>-43.04826858072555,173.07015724176793</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>-43.048256055793324,173.06921709656743</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>-43.048214457218656,173.0682968008122</t>
+        </is>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>-43.048310658761636,173.067382223599</t>
+        </is>
+      </c>
+      <c r="H744" t="inlineStr">
+        <is>
+          <t>-43.04830364598323,173.06647206581354</t>
+        </is>
+      </c>
+      <c r="I744" t="inlineStr">
+        <is>
+          <t>-43.04831810161703,173.06557367735465</t>
+        </is>
+      </c>
+      <c r="J744" t="inlineStr">
+        <is>
+          <t>-43.04836089095083,173.0646771275081</t>
+        </is>
+      </c>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0416/nzd0416.xlsx
+++ b/data/nzd0416/nzd0416.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K744"/>
+  <dimension ref="A1:K747"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29420,6 +29420,123 @@
         <v>317.49</v>
       </c>
       <c r="K744" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:12:53+00:00</t>
+        </is>
+      </c>
+      <c r="B745" t="n">
+        <v>312.59</v>
+      </c>
+      <c r="C745" t="n">
+        <v>304.81</v>
+      </c>
+      <c r="D745" t="n">
+        <v>300.84</v>
+      </c>
+      <c r="E745" t="n">
+        <v>309.7</v>
+      </c>
+      <c r="F745" t="n">
+        <v>307.26</v>
+      </c>
+      <c r="G745" t="n">
+        <v>319.97</v>
+      </c>
+      <c r="H745" t="n">
+        <v>316.6</v>
+      </c>
+      <c r="I745" t="n">
+        <v>314.75</v>
+      </c>
+      <c r="J745" t="n">
+        <v>316.05</v>
+      </c>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:06:54+00:00</t>
+        </is>
+      </c>
+      <c r="B746" t="n">
+        <v>312.1</v>
+      </c>
+      <c r="C746" t="n">
+        <v>304.81</v>
+      </c>
+      <c r="D746" t="n">
+        <v>299.02</v>
+      </c>
+      <c r="E746" t="n">
+        <v>307.81</v>
+      </c>
+      <c r="F746" t="n">
+        <v>304.74</v>
+      </c>
+      <c r="G746" t="n">
+        <v>317.77</v>
+      </c>
+      <c r="H746" t="n">
+        <v>315.07</v>
+      </c>
+      <c r="I746" t="n">
+        <v>313.22</v>
+      </c>
+      <c r="J746" t="n">
+        <v>314.41</v>
+      </c>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:11+00:00</t>
+        </is>
+      </c>
+      <c r="B747" t="n">
+        <v>311.05</v>
+      </c>
+      <c r="C747" t="n">
+        <v>302.65</v>
+      </c>
+      <c r="D747" t="n">
+        <v>297.14</v>
+      </c>
+      <c r="E747" t="n">
+        <v>305.87</v>
+      </c>
+      <c r="F747" t="n">
+        <v>302.27</v>
+      </c>
+      <c r="G747" t="n">
+        <v>315.92</v>
+      </c>
+      <c r="H747" t="n">
+        <v>313.56</v>
+      </c>
+      <c r="I747" t="n">
+        <v>311.62</v>
+      </c>
+      <c r="J747" t="n">
+        <v>312.52</v>
+      </c>
+      <c r="K747" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29436,7 +29553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B836"/>
+  <dimension ref="A1:B839"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37799,6 +37916,36 @@
       </c>
       <c r="B836" t="n">
         <v>0.06</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B837" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B838" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B839" t="n">
+        <v>-0.14</v>
       </c>
     </row>
   </sheetData>
@@ -37967,28 +38114,28 @@
         <v>0.0689</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5983348518196107</v>
+        <v>-0.6009675940440363</v>
       </c>
       <c r="J2" t="n">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="K2" t="n">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08040705490135913</v>
+        <v>0.08169360326150255</v>
       </c>
       <c r="M2" t="n">
-        <v>13.21224722274045</v>
+        <v>13.17186801824132</v>
       </c>
       <c r="N2" t="n">
-        <v>240.1989488624846</v>
+        <v>239.2814003120154</v>
       </c>
       <c r="O2" t="n">
-        <v>15.49835310161969</v>
+        <v>15.46872329289057</v>
       </c>
       <c r="P2" t="n">
-        <v>331.3808164224261</v>
+        <v>331.4079639855224</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -38045,28 +38192,28 @@
         <v>0.07149999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.769770275657509</v>
+        <v>-0.7767137186594443</v>
       </c>
       <c r="J3" t="n">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="K3" t="n">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07386377018957258</v>
+        <v>0.07565492413900443</v>
       </c>
       <c r="M3" t="n">
-        <v>17.27118913557995</v>
+        <v>17.2377201657137</v>
       </c>
       <c r="N3" t="n">
-        <v>435.8596871749703</v>
+        <v>434.4363530887795</v>
       </c>
       <c r="O3" t="n">
-        <v>20.87725286466038</v>
+        <v>20.84313683419028</v>
       </c>
       <c r="P3" t="n">
-        <v>333.7677550938099</v>
+        <v>333.8393502886429</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -38123,28 +38270,28 @@
         <v>0.06660000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5736589088527961</v>
+        <v>-0.5798110981129037</v>
       </c>
       <c r="J4" t="n">
+        <v>746</v>
+      </c>
+      <c r="K4" t="n">
         <v>743</v>
       </c>
-      <c r="K4" t="n">
-        <v>740</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.02177160124054023</v>
+        <v>0.02241434662531683</v>
       </c>
       <c r="M4" t="n">
-        <v>25.43633569511018</v>
+        <v>25.36632837891356</v>
       </c>
       <c r="N4" t="n">
-        <v>860.2281533319544</v>
+        <v>857.0164224219209</v>
       </c>
       <c r="O4" t="n">
-        <v>29.3296463212899</v>
+        <v>29.27484282488842</v>
       </c>
       <c r="P4" t="n">
-        <v>322.3293586155848</v>
+        <v>322.3932352560744</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -38201,28 +38348,28 @@
         <v>0.07149999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6315315011154534</v>
+        <v>-0.634580632827028</v>
       </c>
       <c r="J5" t="n">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="K5" t="n">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03561457411594515</v>
+        <v>0.03624657223714045</v>
       </c>
       <c r="M5" t="n">
-        <v>21.76923816623341</v>
+        <v>21.69784541898483</v>
       </c>
       <c r="N5" t="n">
-        <v>628.2595699466541</v>
+        <v>625.7980279488012</v>
       </c>
       <c r="O5" t="n">
-        <v>25.06510662148985</v>
+        <v>25.0159554674372</v>
       </c>
       <c r="P5" t="n">
-        <v>328.6615740076869</v>
+        <v>328.6932195882901</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -38279,28 +38426,28 @@
         <v>0.0738</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.635395627388467</v>
+        <v>-0.6369437704957794</v>
       </c>
       <c r="J6" t="n">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="K6" t="n">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03248517943788065</v>
+        <v>0.03291367703259196</v>
       </c>
       <c r="M6" t="n">
-        <v>23.04428968202635</v>
+        <v>22.96102518232948</v>
       </c>
       <c r="N6" t="n">
-        <v>699.498830814957</v>
+        <v>696.7108870893813</v>
       </c>
       <c r="O6" t="n">
-        <v>26.44804020745123</v>
+        <v>26.39528153078465</v>
       </c>
       <c r="P6" t="n">
-        <v>323.7876637721799</v>
+        <v>323.8037352272059</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -38357,28 +38504,28 @@
         <v>0.07820000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4992384646706116</v>
+        <v>-0.5006570874595987</v>
       </c>
       <c r="J7" t="n">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="K7" t="n">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04092578152621185</v>
+        <v>0.04149196145509537</v>
       </c>
       <c r="M7" t="n">
-        <v>15.90228573372133</v>
+        <v>15.84679142574594</v>
       </c>
       <c r="N7" t="n">
-        <v>339.779760474221</v>
+        <v>338.4340888069993</v>
       </c>
       <c r="O7" t="n">
-        <v>18.43311586450378</v>
+        <v>18.39657818201524</v>
       </c>
       <c r="P7" t="n">
-        <v>333.0983121038566</v>
+        <v>333.1130382122285</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -38435,28 +38582,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3952446159203136</v>
+        <v>-0.3969869318691774</v>
       </c>
       <c r="J8" t="n">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="K8" t="n">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02111475351176806</v>
+        <v>0.02147869021371707</v>
       </c>
       <c r="M8" t="n">
-        <v>17.72746847464209</v>
+        <v>17.66540635289727</v>
       </c>
       <c r="N8" t="n">
-        <v>421.3120544941464</v>
+        <v>419.6396203035999</v>
       </c>
       <c r="O8" t="n">
-        <v>20.52588742281674</v>
+        <v>20.48510728074422</v>
       </c>
       <c r="P8" t="n">
-        <v>327.9244690074436</v>
+        <v>327.942552829613</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -38513,28 +38660,28 @@
         <v>0.06270000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3402286463655925</v>
+        <v>-0.3434591335696336</v>
       </c>
       <c r="J9" t="n">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="K9" t="n">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01400616909801755</v>
+        <v>0.01439058682182293</v>
       </c>
       <c r="M9" t="n">
-        <v>18.77271259573754</v>
+        <v>18.71483020099853</v>
       </c>
       <c r="N9" t="n">
-        <v>474.0485034768892</v>
+        <v>472.2131193199422</v>
       </c>
       <c r="O9" t="n">
-        <v>21.77265494782134</v>
+        <v>21.73046523477908</v>
       </c>
       <c r="P9" t="n">
-        <v>326.4896927977985</v>
+        <v>326.5232193734881</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -38591,28 +38738,28 @@
         <v>0.0471</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3561797662030994</v>
+        <v>-0.3585962607474918</v>
       </c>
       <c r="J10" t="n">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="K10" t="n">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01047936968732921</v>
+        <v>0.01071127118929727</v>
       </c>
       <c r="M10" t="n">
-        <v>22.9031107429623</v>
+        <v>22.82343692142227</v>
       </c>
       <c r="N10" t="n">
-        <v>708.604641162696</v>
+        <v>705.7762666849524</v>
       </c>
       <c r="O10" t="n">
-        <v>26.61962886974001</v>
+        <v>26.56645002037255</v>
       </c>
       <c r="P10" t="n">
-        <v>327.022220568636</v>
+        <v>327.0470682165046</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -38650,7 +38797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K744"/>
+  <dimension ref="A1:K747"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80981,6 +81128,177 @@
         </is>
       </c>
     </row>
+    <row r="745">
+      <c r="A745" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:12:53+00:00</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>-43.04862266922188,173.07191041344268</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>-43.04842186111794,173.07104969678295</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>-43.04825215702348,173.07016104816435</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>-43.04823963684754,173.06921901578696</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>-43.04819204504522,173.06829772757055</t>
+        </is>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>-43.04829048898024,173.0673818945893</t>
+        </is>
+      </c>
+      <c r="H745" t="inlineStr">
+        <is>
+          <t>-43.04829123312099,173.06647126022364</t>
+        </is>
+      </c>
+      <c r="I745" t="inlineStr">
+        <is>
+          <t>-43.048305418905514,173.06557285437634</t>
+        </is>
+      </c>
+      <c r="J745" t="inlineStr">
+        <is>
+          <t>-43.04834793838994,173.06467628714594</t>
+        </is>
+      </c>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:06:54+00:00</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>-43.04861834682707,173.0719116227877</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>-43.04842186111794,173.07104969678295</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>-43.048235999651574,173.07016479283342</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>-43.04822267957558,173.06922099793067</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>-43.04816936284548,173.06829866549404</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>-43.04827067937346,173.06738157145497</t>
+        </is>
+      </c>
+      <c r="H746" t="inlineStr">
+        <is>
+          <t>-43.04827747103456,173.06647036707002</t>
+        </is>
+      </c>
+      <c r="I746" t="inlineStr">
+        <is>
+          <t>-43.04829165681427,173.06557196135776</t>
+        </is>
+      </c>
+      <c r="J746" t="inlineStr">
+        <is>
+          <t>-43.04833318686221,173.06467533006725</t>
+        </is>
+      </c>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:11+00:00</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>-43.048609084552425,173.0719142142407</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>-43.04840280732166,173.07105502793198</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>-43.04821930961886,173.07016866095108</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>-43.04820527369846,173.06922303251093</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>-43.0481471306893,173.06829958480722</t>
+        </is>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>-43.04825402129497,173.06738129972854</t>
+        </is>
+      </c>
+      <c r="H747" t="inlineStr">
+        <is>
+          <t>-43.04826388884463,173.066469485592</t>
+        </is>
+      </c>
+      <c r="I747" t="inlineStr">
+        <is>
+          <t>-43.048277265084806,173.06557102748252</t>
+        </is>
+      </c>
+      <c r="J747" t="inlineStr">
+        <is>
+          <t>-43.04831618662595,173.06467422709298</t>
+        </is>
+      </c>
+      <c r="K747" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
